--- a/eval/qlora/evaluation_metrics_by_qid_full150.xlsx
+++ b/eval/qlora/evaluation_metrics_by_qid_full150.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,32 +547,32 @@
         <v>150</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9215686274509803</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9215686274509803</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9215686274509803</v>
+        <v>0.8854166666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -594,32 +594,32 @@
         <v>150</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9204545454545454</v>
+        <v>0.9215686274509803</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.9215686274509803</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8526315789473684</v>
+        <v>0.9215686274509803</v>
       </c>
       <c r="F4" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -641,19 +641,19 @@
         <v>150</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9135802469135802</v>
+        <v>0.9204545454545454</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7254901960784313</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8087431693989071</v>
+        <v>0.8526315789473684</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
         <v>41</v>
@@ -662,11 +662,11 @@
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -688,32 +688,32 @@
         <v>150</v>
       </c>
       <c r="B6" t="n">
-        <v>0.86</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9135802469135802</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.7254901960784313</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8955223880597014</v>
+        <v>0.8087431693989071</v>
       </c>
       <c r="F6" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -735,32 +735,32 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9183673469387755</v>
+        <v>0.9278350515463918</v>
       </c>
       <c r="D7" t="n">
         <v>0.8823529411764706</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>0.9045226130653266</v>
       </c>
       <c r="F7" t="n">
         <v>90</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
         <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -782,36 +782,36 @@
         <v>150</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.86</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8727272727272727</v>
+        <v>0.8955223880597014</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-8B R16</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
     </row>
@@ -829,36 +829,36 @@
         <v>150</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.9183673469387755</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8363636363636364</v>
+        <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-8B R32</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
     </row>
@@ -876,32 +876,32 @@
         <v>150</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8214285714285715</v>
+        <v>0.8727272727272727</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-70B FT</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -923,32 +923,32 @@
         <v>150</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="C11" t="n">
-        <v>0.875</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.823529411764706</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -970,32 +970,32 @@
         <v>150</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.8363636363636364</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1017,32 +1017,32 @@
         <v>150</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.8214285714285715</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1064,36 +1064,36 @@
         <v>150</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.823529411764706</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" t="n">
         <v>120</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>6</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
     </row>
@@ -1111,36 +1111,36 @@
         <v>150</v>
       </c>
       <c r="B15" t="n">
-        <v>0.96</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.6052631578947368</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.7076923076923076</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
     </row>
@@ -1158,36 +1158,36 @@
         <v>150</v>
       </c>
       <c r="B16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C16" t="n">
-        <v>0.88</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8301886792452829</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-8B R16</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
     </row>
@@ -1205,36 +1205,36 @@
         <v>150</v>
       </c>
       <c r="B17" t="n">
-        <v>0.86</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6440677966101694</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>110</v>
       </c>
       <c r="H17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
         <v>9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-8B R32</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
     </row>
@@ -1252,32 +1252,32 @@
         <v>150</v>
       </c>
       <c r="B18" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7037037037037037</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6909090909090909</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-70B FT</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1299,32 +1299,32 @@
         <v>150</v>
       </c>
       <c r="B19" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.75</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7096774193548386</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1346,45 +1346,45 @@
         <v>150</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9866666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
     </row>
@@ -1393,45 +1393,45 @@
         <v>150</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9866666666666667</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.88</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.8301886792452829</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
     </row>
@@ -1440,45 +1440,45 @@
         <v>150</v>
       </c>
       <c r="B22" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="E22" t="n">
-        <v>0.85</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
     </row>
@@ -1487,45 +1487,45 @@
         <v>150</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.53125</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F23" t="n">
+        <v>17</v>
+      </c>
+      <c r="G23" t="n">
+        <v>107</v>
+      </c>
+      <c r="H23" t="n">
         <v>15</v>
       </c>
-      <c r="G23" t="n">
-        <v>128</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
     </row>
@@ -1534,28 +1534,28 @@
         <v>150</v>
       </c>
       <c r="B24" t="n">
-        <v>0.92</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.6909090909090909</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
     </row>
@@ -1581,25 +1581,25 @@
         <v>150</v>
       </c>
       <c r="B25" t="n">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8421052631578948</v>
+        <v>0.7096774193548386</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
         <v>6</v>
@@ -1610,16 +1610,16 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
     </row>
@@ -1628,28 +1628,28 @@
         <v>150</v>
       </c>
       <c r="B26" t="n">
-        <v>0.8</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="F26" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1657,16 +1657,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
     </row>
@@ -1675,45 +1675,45 @@
         <v>150</v>
       </c>
       <c r="B27" t="n">
-        <v>0.82</v>
+        <v>0.9933333333333333</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9866666666666667</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D27" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8457142857142858</v>
+        <v>0.9777777777777777</v>
       </c>
       <c r="F27" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
     </row>
@@ -1722,45 +1722,45 @@
         <v>150</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="C28" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="F28" t="n">
+        <v>21</v>
+      </c>
+      <c r="G28" t="n">
+        <v>127</v>
+      </c>
+      <c r="H28" t="n">
         <v>1</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.7421383647798743</v>
-      </c>
-      <c r="F28" t="n">
-        <v>59</v>
-      </c>
-      <c r="G28" t="n">
-        <v>50</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
     </row>
@@ -1769,45 +1769,45 @@
         <v>150</v>
       </c>
       <c r="B29" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.96</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="D29" t="n">
-        <v>0.63</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7590361445783134</v>
+        <v>0.85</v>
       </c>
       <c r="F29" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
     </row>
@@ -1816,45 +1816,45 @@
         <v>150</v>
       </c>
       <c r="B30" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8974358974358975</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7865168539325842</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="F30" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
     </row>
@@ -1863,45 +1863,45 @@
         <v>150</v>
       </c>
       <c r="B31" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="C31" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.72</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="F31" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="G31" t="n">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
     </row>
@@ -1910,36 +1910,36 @@
         <v>150</v>
       </c>
       <c r="B32" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.92</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9605263157894737</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8111111111111111</v>
+        <v>0.5</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8795180722891566</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="F32" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-8B R16</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
     </row>
@@ -1957,37 +1957,37 @@
         <v>150</v>
       </c>
       <c r="B33" t="n">
-        <v>0.9133333333333333</v>
+        <v>0.96</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9529411764705882</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9257142857142857</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="F33" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R32</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
         <v>4</v>
       </c>
-      <c r="I33" t="n">
-        <v>9</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B R16</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>6</v>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>List</t>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
     </row>
@@ -2004,45 +2004,45 @@
         <v>150</v>
       </c>
       <c r="B34" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9428571428571428</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8250000000000001</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="F34" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G34" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-70B FT</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
     </row>
@@ -2051,45 +2051,45 @@
         <v>150</v>
       </c>
       <c r="B35" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9404761904761905</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.79</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.858695652173913</v>
       </c>
       <c r="F35" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G35" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
     </row>
@@ -2098,45 +2098,45 @@
         <v>150</v>
       </c>
       <c r="B36" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.9866666666666667</v>
+      </c>
+      <c r="D36" t="n">
         <v>0.74</v>
       </c>
-      <c r="C36" t="n">
-        <v>0.8923076923076924</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.6444444444444445</v>
-      </c>
       <c r="E36" t="n">
-        <v>0.7483870967741936</v>
+        <v>0.8457142857142858</v>
       </c>
       <c r="F36" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="G36" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
     </row>
@@ -2145,45 +2145,45 @@
         <v>150</v>
       </c>
       <c r="B37" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9264705882352942</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7974683544303798</v>
+        <v>0.7421383647798743</v>
       </c>
       <c r="F37" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G37" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>41</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R32</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>5</v>
       </c>
-      <c r="I37" t="n">
-        <v>27</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B R32</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>6</v>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
     </row>
@@ -2192,45 +2192,45 @@
         <v>150</v>
       </c>
       <c r="B38" t="n">
-        <v>0.86</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8662420382165604</v>
+        <v>0.7590361445783134</v>
       </c>
       <c r="F38" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G38" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
     </row>
@@ -2239,45 +2239,45 @@
         <v>150</v>
       </c>
       <c r="B39" t="n">
-        <v>0.92</v>
+        <v>0.74</v>
       </c>
       <c r="C39" t="n">
-        <v>0.974025974025974</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.67</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9259259259259258</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="F39" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="G39" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
     </row>
@@ -2286,45 +2286,45 @@
         <v>150</v>
       </c>
       <c r="B40" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7294117647058823</v>
+        <v>0.7</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.7865168539325842</v>
       </c>
       <c r="F40" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G40" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-8B R16</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
     </row>
@@ -2333,45 +2333,45 @@
         <v>150</v>
       </c>
       <c r="B41" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9636363636363636</v>
+        <v>0.96</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6235294117647059</v>
+        <v>0.72</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7571428571428571</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="F41" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G41" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-8B R32</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
     </row>
@@ -2380,37 +2380,37 @@
         <v>150</v>
       </c>
       <c r="B42" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9605263157894737</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7947019867549669</v>
+        <v>0.8795180722891566</v>
       </c>
       <c r="F42" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G42" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>17</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>6</v>
       </c>
-      <c r="I42" t="n">
-        <v>25</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B R16</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>7</v>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>List</t>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2427,36 +2427,36 @@
         <v>150</v>
       </c>
       <c r="B43" t="n">
-        <v>0.8</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9365079365079365</v>
+        <v>0.9506172839506173</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6941176470588235</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7972972972972974</v>
+        <v>0.9005847953216374</v>
       </c>
       <c r="F43" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="G43" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H43" t="n">
         <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2474,45 +2474,45 @@
         <v>150</v>
       </c>
       <c r="B44" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.9133333333333333</v>
       </c>
       <c r="C44" t="n">
-        <v>0.75</v>
+        <v>0.9529411764705882</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.9257142857142857</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="G44" t="n">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
+        <v>9</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R16</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
         <v>6</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B FT</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>8</v>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2521,45 +2521,45 @@
         <v>150</v>
       </c>
       <c r="B45" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="G45" t="n">
-        <v>138</v>
+        <v>56</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2568,45 +2568,45 @@
         <v>150</v>
       </c>
       <c r="B46" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="G46" t="n">
-        <v>139</v>
+        <v>56</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2615,45 +2615,45 @@
         <v>150</v>
       </c>
       <c r="B47" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.72</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4</v>
+        <v>0.8870967741935484</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.7236842105263158</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="G47" t="n">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I47" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2662,28 +2662,28 @@
         <v>150</v>
       </c>
       <c r="B48" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.74</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8923076923076924</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5</v>
+        <v>0.7483870967741936</v>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="G48" t="n">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2709,28 +2709,28 @@
         <v>150</v>
       </c>
       <c r="B49" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4</v>
+        <v>0.9264705882352942</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.7</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.7974683544303798</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="G49" t="n">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2738,16 +2738,16 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2756,28 +2756,28 @@
         <v>150</v>
       </c>
       <c r="B50" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.86</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9879518072289156</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="D50" t="n">
-        <v>0.656</v>
+        <v>0.8</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7884615384615384</v>
+        <v>0.8662420382165604</v>
       </c>
       <c r="F50" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G50" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I50" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2803,36 +2803,36 @@
         <v>150</v>
       </c>
       <c r="B51" t="n">
-        <v>0.74</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9673913043478261</v>
+        <v>0.9367088607594937</v>
       </c>
       <c r="D51" t="n">
-        <v>0.712</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8202764976958525</v>
+        <v>0.9024390243902438</v>
       </c>
       <c r="F51" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G51" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2850,36 +2850,36 @@
         <v>150</v>
       </c>
       <c r="B52" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.92</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="D52" t="n">
-        <v>0.64</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7619047619047621</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="F52" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G52" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2897,36 +2897,36 @@
         <v>150</v>
       </c>
       <c r="B53" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="D53" t="n">
-        <v>0.472</v>
+        <v>0.7294117647058823</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6378378378378378</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F53" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G53" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2944,36 +2944,36 @@
         <v>150</v>
       </c>
       <c r="B54" t="n">
-        <v>0.62</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9636363636363636</v>
       </c>
       <c r="D54" t="n">
-        <v>0.576</v>
+        <v>0.6235294117647059</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7164179104477613</v>
+        <v>0.7571428571428571</v>
       </c>
       <c r="F54" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G54" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -2991,36 +2991,36 @@
         <v>150</v>
       </c>
       <c r="B55" t="n">
-        <v>0.68</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9753086419753086</v>
+        <v>0.8805970149253731</v>
       </c>
       <c r="D55" t="n">
-        <v>0.632</v>
+        <v>0.6941176470588235</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7669902912621359</v>
+        <v>0.7763157894736843</v>
       </c>
       <c r="F55" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="G55" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I55" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -3038,36 +3038,36 @@
         <v>150</v>
       </c>
       <c r="B56" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9682539682539683</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="D56" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8472222222222222</v>
+        <v>0.7947019867549669</v>
       </c>
       <c r="F56" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G56" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-8B R16</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -3085,36 +3085,36 @@
         <v>150</v>
       </c>
       <c r="B57" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9852941176470589</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.6941176470588235</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8993288590604026</v>
+        <v>0.7972972972972974</v>
       </c>
       <c r="F57" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G57" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I57" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-8B R32</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
     </row>
@@ -3132,45 +3132,45 @@
         <v>150</v>
       </c>
       <c r="B58" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9827586206896551</v>
+        <v>0.75</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7037037037037037</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8201438848920862</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="F58" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G58" t="n">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="H58" t="n">
         <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-70B FT</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
     </row>
@@ -3179,45 +3179,45 @@
         <v>150</v>
       </c>
       <c r="B59" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5679012345679012</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6917293233082706</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F59" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="H59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I59" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
     </row>
@@ -3226,45 +3226,45 @@
         <v>150</v>
       </c>
       <c r="B60" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9107142857142857</v>
+        <v>0.4</v>
       </c>
       <c r="D60" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7445255474452555</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F60" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G60" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I60" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
     </row>
@@ -3273,45 +3273,45 @@
         <v>150</v>
       </c>
       <c r="B61" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.5</v>
       </c>
       <c r="D61" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="F61" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
     </row>
@@ -3320,45 +3320,45 @@
         <v>150</v>
       </c>
       <c r="B62" t="n">
-        <v>0.8</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.4</v>
       </c>
       <c r="D62" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E62" t="n">
-        <v>0.810126582278481</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F62" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
     </row>
@@ -3367,45 +3367,45 @@
         <v>150</v>
       </c>
       <c r="B63" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.9266666666666666</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9178082191780822</v>
+        <v>0.375</v>
       </c>
       <c r="D63" t="n">
-        <v>0.7282608695652174</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8121212121212121</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="F63" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="H63" t="n">
+        <v>5</v>
+      </c>
+      <c r="I63" t="n">
         <v>6</v>
       </c>
-      <c r="I63" t="n">
-        <v>25</v>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
     </row>
@@ -3414,45 +3414,45 @@
         <v>150</v>
       </c>
       <c r="B64" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="C64" t="n">
-        <v>0.921875</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D64" t="n">
-        <v>0.6413043478260869</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7564102564102563</v>
+        <v>0.5</v>
       </c>
       <c r="F64" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="H64" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" t="n">
         <v>5</v>
       </c>
-      <c r="I64" t="n">
-        <v>33</v>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-8B R16</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
     </row>
@@ -3461,45 +3461,45 @@
         <v>150</v>
       </c>
       <c r="B65" t="n">
-        <v>0.7</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9122807017543859</v>
+        <v>0.4</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6979865771812079</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F65" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="H65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-8B R32</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
     </row>
@@ -3508,36 +3508,36 @@
         <v>150</v>
       </c>
       <c r="B66" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9879518072289156</v>
       </c>
       <c r="D66" t="n">
-        <v>0.6195652173913043</v>
+        <v>0.656</v>
       </c>
       <c r="E66" t="n">
-        <v>0.735483870967742</v>
+        <v>0.7884615384615384</v>
       </c>
       <c r="F66" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="G66" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="H66" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-70B FT</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
     </row>
@@ -3555,36 +3555,36 @@
         <v>150</v>
       </c>
       <c r="B67" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8833333333333333</v>
+        <v>0.9252336448598131</v>
       </c>
       <c r="D67" t="n">
-        <v>0.5760869565217391</v>
+        <v>0.792</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6973684210526314</v>
+        <v>0.8534482758620691</v>
       </c>
       <c r="F67" t="n">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="G67" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="H67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I67" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
     </row>
@@ -3602,45 +3602,45 @@
         <v>150</v>
       </c>
       <c r="B68" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9673913043478261</v>
       </c>
       <c r="D68" t="n">
-        <v>0.6229508196721312</v>
+        <v>0.712</v>
       </c>
       <c r="E68" t="n">
-        <v>0.76</v>
+        <v>0.8202764976958525</v>
       </c>
       <c r="F68" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="G68" t="n">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
     </row>
@@ -3649,45 +3649,45 @@
         <v>150</v>
       </c>
       <c r="B69" t="n">
-        <v>0.8733333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7213114754098361</v>
+        <v>0.64</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8224299065420561</v>
+        <v>0.7619047619047621</v>
       </c>
       <c r="F69" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="G69" t="n">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
     </row>
@@ -3696,45 +3696,45 @@
         <v>150</v>
       </c>
       <c r="B70" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.5533333333333333</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="D70" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.472</v>
       </c>
       <c r="E70" t="n">
-        <v>0.74</v>
+        <v>0.6378378378378378</v>
       </c>
       <c r="F70" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="G70" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
     </row>
@@ -3743,45 +3743,45 @@
         <v>150</v>
       </c>
       <c r="B71" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="D71" t="n">
-        <v>0.5901639344262295</v>
+        <v>0.592</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.729064039408867</v>
       </c>
       <c r="F71" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="G71" t="n">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
     </row>
@@ -3790,28 +3790,28 @@
         <v>150</v>
       </c>
       <c r="B72" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="C72" t="n">
-        <v>0.9347826086956522</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D72" t="n">
-        <v>0.7049180327868853</v>
+        <v>0.576</v>
       </c>
       <c r="E72" t="n">
-        <v>0.8037383177570093</v>
+        <v>0.7164179104477613</v>
       </c>
       <c r="F72" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G72" t="n">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="H72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3819,16 +3819,16 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
     </row>
@@ -3837,28 +3837,28 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.68</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="D73" t="n">
-        <v>0.5573770491803278</v>
+        <v>0.632</v>
       </c>
       <c r="E73" t="n">
-        <v>0.686868686868687</v>
+        <v>0.7669902912621359</v>
       </c>
       <c r="F73" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="G73" t="n">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="H73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3866,16 +3866,16 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
     </row>
@@ -3884,28 +3884,28 @@
         <v>150</v>
       </c>
       <c r="B74" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9682539682539683</v>
       </c>
       <c r="D74" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9</v>
+        <v>0.8472222222222222</v>
       </c>
       <c r="F74" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="G74" t="n">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3913,16 +3913,16 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
     </row>
@@ -3931,45 +3931,45 @@
         <v>150</v>
       </c>
       <c r="B75" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C75" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.861111111111111</v>
       </c>
       <c r="F75" t="n">
+        <v>62</v>
+      </c>
+      <c r="G75" t="n">
+        <v>68</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
         <v>19</v>
       </c>
-      <c r="G75" t="n">
-        <v>127</v>
-      </c>
-      <c r="H75" t="n">
-        <v>2</v>
-      </c>
-      <c r="I75" t="n">
-        <v>2</v>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
     </row>
@@ -3978,45 +3978,45 @@
         <v>150</v>
       </c>
       <c r="B76" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.9852941176470589</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8993288590604026</v>
       </c>
       <c r="F76" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="G76" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
     </row>
@@ -4025,45 +4025,45 @@
         <v>150</v>
       </c>
       <c r="B77" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9827586206896551</v>
       </c>
       <c r="D77" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="E77" t="n">
-        <v>0.742857142857143</v>
+        <v>0.8201438848920862</v>
       </c>
       <c r="F77" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="G77" t="n">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
     </row>
@@ -4072,45 +4072,45 @@
         <v>150</v>
       </c>
       <c r="B78" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="C78" t="n">
-        <v>0.9375</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5679012345679012</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.6917293233082706</v>
       </c>
       <c r="F78" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G78" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I78" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
     </row>
@@ -4119,45 +4119,45 @@
         <v>150</v>
       </c>
       <c r="B79" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.76</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8813559322033898</v>
       </c>
       <c r="D79" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.6419753086419753</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.7428571428571428</v>
       </c>
       <c r="F79" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G79" t="n">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
     </row>
@@ -4166,45 +4166,45 @@
         <v>150</v>
       </c>
       <c r="B80" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9811320754716981</v>
+        <v>0.9107142857142857</v>
       </c>
       <c r="D80" t="n">
-        <v>0.7123287671232876</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8253968253968254</v>
+        <v>0.7445255474452555</v>
       </c>
       <c r="F80" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G80" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-8B R16</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
     </row>
@@ -4213,45 +4213,45 @@
         <v>150</v>
       </c>
       <c r="B81" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9482758620689655</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D81" t="n">
-        <v>0.7534246575342466</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E81" t="n">
-        <v>0.8396946564885496</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="F81" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G81" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H81" t="n">
         <v>3</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-8B R32</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
     </row>
@@ -4263,42 +4263,42 @@
         <v>0.8</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6575342465753424</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="E82" t="n">
-        <v>0.761904761904762</v>
+        <v>0.810126582278481</v>
       </c>
       <c r="F82" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G82" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-70B FT</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
     </row>
@@ -4307,45 +4307,45 @@
         <v>150</v>
       </c>
       <c r="B83" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.7533333333333333</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8313253012048193</v>
       </c>
       <c r="D83" t="n">
-        <v>0.6575342465753424</v>
+        <v>0.75</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7559055118110236</v>
+        <v>0.7885714285714285</v>
       </c>
       <c r="F83" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="G83" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H83" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
     </row>
@@ -4354,45 +4354,45 @@
         <v>150</v>
       </c>
       <c r="B84" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8301886792452831</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="D84" t="n">
-        <v>0.6027397260273972</v>
+        <v>0.7282608695652174</v>
       </c>
       <c r="E84" t="n">
-        <v>0.6984126984126985</v>
+        <v>0.8121212121212121</v>
       </c>
       <c r="F84" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="G84" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H84" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
     </row>
@@ -4401,45 +4401,45 @@
         <v>150</v>
       </c>
       <c r="B85" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="C85" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.921875</v>
       </c>
       <c r="D85" t="n">
-        <v>0.589041095890411</v>
+        <v>0.6413043478260869</v>
       </c>
       <c r="E85" t="n">
-        <v>0.6771653543307086</v>
+        <v>0.7564102564102563</v>
       </c>
       <c r="F85" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G85" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="H85" t="n">
+        <v>5</v>
+      </c>
+      <c r="I85" t="n">
+        <v>33</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R32</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
         <v>11</v>
       </c>
-      <c r="I85" t="n">
-        <v>30</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B R32</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
-        <v>14</v>
-      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
     </row>
@@ -4448,37 +4448,37 @@
         <v>150</v>
       </c>
       <c r="B86" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.9122807017543859</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5522388059701493</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="E86" t="n">
-        <v>0.6434782608695653</v>
+        <v>0.6979865771812079</v>
       </c>
       <c r="F86" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G86" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="H86" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>40</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
         <v>11</v>
       </c>
-      <c r="I86" t="n">
-        <v>30</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B FT</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>15</v>
-      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>List</t>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
     </row>
@@ -4495,36 +4495,36 @@
         <v>150</v>
       </c>
       <c r="B87" t="n">
-        <v>0.78</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="C87" t="n">
-        <v>0.84</v>
+        <v>0.875</v>
       </c>
       <c r="D87" t="n">
-        <v>0.6268656716417911</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7179487179487181</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="F87" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G87" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H87" t="n">
         <v>8</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
     </row>
@@ -4542,37 +4542,37 @@
         <v>150</v>
       </c>
       <c r="B88" t="n">
-        <v>0.76</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="C88" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="D88" t="n">
-        <v>0.6268656716417911</v>
+        <v>0.6195652173913043</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.735483870967742</v>
       </c>
       <c r="F88" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G88" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="H88" t="n">
+        <v>6</v>
+      </c>
+      <c r="I88" t="n">
+        <v>35</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R16</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
         <v>11</v>
       </c>
-      <c r="I88" t="n">
-        <v>25</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B R32</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>15</v>
-      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>List</t>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
     </row>
@@ -4589,36 +4589,36 @@
         <v>150</v>
       </c>
       <c r="B89" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="C89" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="D89" t="n">
-        <v>0.5671641791044776</v>
+        <v>0.5760869565217391</v>
       </c>
       <c r="E89" t="n">
-        <v>0.6386554621848739</v>
+        <v>0.6973684210526314</v>
       </c>
       <c r="F89" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G89" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H89" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I89" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-8B R32</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
     </row>
@@ -4636,45 +4636,45 @@
         <v>150</v>
       </c>
       <c r="B90" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.84</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7884615384615384</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="D90" t="n">
-        <v>0.6119402985074627</v>
+        <v>0.6229508196721312</v>
       </c>
       <c r="E90" t="n">
-        <v>0.6890756302521007</v>
+        <v>0.76</v>
       </c>
       <c r="F90" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G90" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="H90" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-70B FT</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
     </row>
@@ -4683,45 +4683,45 @@
         <v>150</v>
       </c>
       <c r="B91" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="C91" t="n">
-        <v>0.7</v>
+        <v>0.9272727272727272</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5223880597014925</v>
+        <v>0.8360655737704918</v>
       </c>
       <c r="E91" t="n">
-        <v>0.5982905982905983</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="F91" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G91" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="H91" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I91" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
     </row>
@@ -4730,45 +4730,45 @@
         <v>150</v>
       </c>
       <c r="B92" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C92" t="n">
-        <v>0.696969696969697</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4035087719298245</v>
+        <v>0.7213114754098361</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.8224299065420561</v>
       </c>
       <c r="F92" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G92" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H92" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Llama3.1-70B FT</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
     </row>
@@ -4777,45 +4777,45 @@
         <v>150</v>
       </c>
       <c r="B93" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C93" t="n">
-        <v>0.71875</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4035087719298245</v>
+        <v>0.6065573770491803</v>
       </c>
       <c r="E93" t="n">
-        <v>0.5168539325842696</v>
+        <v>0.74</v>
       </c>
       <c r="F93" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G93" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H93" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
     </row>
@@ -4824,45 +4824,45 @@
         <v>150</v>
       </c>
       <c r="B94" t="n">
-        <v>0.74</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C94" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4912280701754386</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="E94" t="n">
-        <v>0.5894736842105264</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="F94" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G94" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H94" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I94" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
     </row>
@@ -4871,45 +4871,45 @@
         <v>150</v>
       </c>
       <c r="B95" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C95" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.9183673469387755</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2807017543859649</v>
+        <v>0.7377049180327869</v>
       </c>
       <c r="E95" t="n">
-        <v>0.3764705882352941</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="F95" t="n">
+        <v>45</v>
+      </c>
+      <c r="G95" t="n">
+        <v>85</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4</v>
+      </c>
+      <c r="I95" t="n">
         <v>16</v>
       </c>
-      <c r="G95" t="n">
-        <v>81</v>
-      </c>
-      <c r="H95" t="n">
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R8</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
         <v>12</v>
       </c>
-      <c r="I95" t="n">
-        <v>41</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B FT</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>16</v>
-      </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
     </row>
@@ -4918,28 +4918,28 @@
         <v>150</v>
       </c>
       <c r="B96" t="n">
-        <v>0.66</v>
+        <v>0.86</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.9347826086956522</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3859649122807017</v>
+        <v>0.7049180327868853</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4631578947368421</v>
+        <v>0.8037383177570093</v>
       </c>
       <c r="F96" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G96" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H96" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I96" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4947,16 +4947,16 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
     </row>
@@ -4965,43 +4965,1547 @@
         <v>150</v>
       </c>
       <c r="B97" t="n">
+        <v>0.7933333333333333</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.5573770491803278</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.686868686868687</v>
+      </c>
+      <c r="F97" t="n">
+        <v>34</v>
+      </c>
+      <c r="G97" t="n">
+        <v>85</v>
+      </c>
+      <c r="H97" t="n">
+        <v>4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>27</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R32</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>12</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>150</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0.9733333333333334</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F98" t="n">
+        <v>18</v>
+      </c>
+      <c r="G98" t="n">
+        <v>128</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>3</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>13</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>150</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.8750000000000001</v>
+      </c>
+      <c r="F99" t="n">
+        <v>21</v>
+      </c>
+      <c r="G99" t="n">
+        <v>123</v>
+      </c>
+      <c r="H99" t="n">
+        <v>6</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R8</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>13</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>150</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.9733333333333334</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="F100" t="n">
+        <v>19</v>
+      </c>
+      <c r="G100" t="n">
+        <v>127</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" t="n">
+        <v>2</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R16</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>13</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>150</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="F101" t="n">
+        <v>17</v>
+      </c>
+      <c r="G101" t="n">
+        <v>125</v>
+      </c>
+      <c r="H101" t="n">
+        <v>4</v>
+      </c>
+      <c r="I101" t="n">
+        <v>4</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R32</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>13</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>150</v>
+      </c>
+      <c r="B102" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.742857142857143</v>
+      </c>
+      <c r="F102" t="n">
+        <v>13</v>
+      </c>
+      <c r="G102" t="n">
+        <v>128</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>8</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>13</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>150</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="F103" t="n">
+        <v>18</v>
+      </c>
+      <c r="G103" t="n">
+        <v>127</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>3</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R8</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>13</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>150</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0.9533333333333334</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.8108108108108109</v>
+      </c>
+      <c r="F104" t="n">
+        <v>15</v>
+      </c>
+      <c r="G104" t="n">
+        <v>128</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" t="n">
+        <v>6</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R16</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>13</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>150</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.9533333333333334</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="F105" t="n">
+        <v>16</v>
+      </c>
+      <c r="G105" t="n">
+        <v>127</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" t="n">
+        <v>5</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R32</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>13</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>150</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.9811320754716981</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.7123287671232876</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.8253968253968254</v>
+      </c>
+      <c r="F106" t="n">
+        <v>52</v>
+      </c>
+      <c r="G106" t="n">
+        <v>76</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>21</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>14</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>150</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0.8866666666666667</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.8493150684931506</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.8794326241134752</v>
+      </c>
+      <c r="F107" t="n">
+        <v>62</v>
+      </c>
+      <c r="G107" t="n">
+        <v>71</v>
+      </c>
+      <c r="H107" t="n">
+        <v>6</v>
+      </c>
+      <c r="I107" t="n">
+        <v>11</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R8</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>14</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>150</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.9482758620689655</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.7534246575342466</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.8396946564885496</v>
+      </c>
+      <c r="F108" t="n">
+        <v>55</v>
+      </c>
+      <c r="G108" t="n">
+        <v>74</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" t="n">
+        <v>18</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R16</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>14</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>150</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.6575342465753424</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.761904761904762</v>
+      </c>
+      <c r="F109" t="n">
+        <v>48</v>
+      </c>
+      <c r="G109" t="n">
+        <v>72</v>
+      </c>
+      <c r="H109" t="n">
+        <v>5</v>
+      </c>
+      <c r="I109" t="n">
+        <v>25</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R32</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>14</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>150</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.7933333333333333</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.6575342465753424</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.7559055118110236</v>
+      </c>
+      <c r="F110" t="n">
+        <v>48</v>
+      </c>
+      <c r="G110" t="n">
+        <v>71</v>
+      </c>
+      <c r="H110" t="n">
+        <v>6</v>
+      </c>
+      <c r="I110" t="n">
+        <v>25</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>14</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>150</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.5753424657534246</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.6829268292682927</v>
+      </c>
+      <c r="F111" t="n">
+        <v>42</v>
+      </c>
+      <c r="G111" t="n">
+        <v>69</v>
+      </c>
+      <c r="H111" t="n">
+        <v>8</v>
+      </c>
+      <c r="I111" t="n">
+        <v>31</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R8</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>14</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>150</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.6027397260273972</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.6984126984126985</v>
+      </c>
+      <c r="F112" t="n">
+        <v>44</v>
+      </c>
+      <c r="G112" t="n">
+        <v>68</v>
+      </c>
+      <c r="H112" t="n">
+        <v>9</v>
+      </c>
+      <c r="I112" t="n">
+        <v>29</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R16</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>14</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>150</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0.7266666666666667</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.589041095890411</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.6771653543307086</v>
+      </c>
+      <c r="F113" t="n">
+        <v>43</v>
+      </c>
+      <c r="G113" t="n">
+        <v>66</v>
+      </c>
+      <c r="H113" t="n">
+        <v>11</v>
+      </c>
+      <c r="I113" t="n">
+        <v>30</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R32</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>14</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>150</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0.7266666666666667</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.5522388059701493</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.6434782608695653</v>
+      </c>
+      <c r="F114" t="n">
+        <v>37</v>
+      </c>
+      <c r="G114" t="n">
+        <v>72</v>
+      </c>
+      <c r="H114" t="n">
+        <v>11</v>
+      </c>
+      <c r="I114" t="n">
+        <v>30</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>15</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>150</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.5933333333333334</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.5277777777777778</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.8507462686567164</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.6514285714285716</v>
+      </c>
+      <c r="F115" t="n">
+        <v>57</v>
+      </c>
+      <c r="G115" t="n">
+        <v>32</v>
+      </c>
+      <c r="H115" t="n">
+        <v>51</v>
+      </c>
+      <c r="I115" t="n">
+        <v>10</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R8</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>15</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>150</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.6268656716417911</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.7179487179487181</v>
+      </c>
+      <c r="F116" t="n">
+        <v>42</v>
+      </c>
+      <c r="G116" t="n">
+        <v>75</v>
+      </c>
+      <c r="H116" t="n">
+        <v>8</v>
+      </c>
+      <c r="I116" t="n">
+        <v>25</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R16</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>15</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>150</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6268656716417911</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>42</v>
+      </c>
+      <c r="G117" t="n">
+        <v>72</v>
+      </c>
+      <c r="H117" t="n">
+        <v>11</v>
+      </c>
+      <c r="I117" t="n">
+        <v>25</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R32</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>15</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>150</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.7133333333333334</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.5671641791044776</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6386554621848739</v>
+      </c>
+      <c r="F118" t="n">
+        <v>38</v>
+      </c>
+      <c r="G118" t="n">
+        <v>69</v>
+      </c>
+      <c r="H118" t="n">
+        <v>14</v>
+      </c>
+      <c r="I118" t="n">
+        <v>29</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>15</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>150</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.7266666666666667</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5373134328358209</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6371681415929203</v>
+      </c>
+      <c r="F119" t="n">
+        <v>36</v>
+      </c>
+      <c r="G119" t="n">
+        <v>73</v>
+      </c>
+      <c r="H119" t="n">
+        <v>10</v>
+      </c>
+      <c r="I119" t="n">
+        <v>31</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R8</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>15</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>150</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.7533333333333333</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.7884615384615384</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.6119402985074627</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.6890756302521007</v>
+      </c>
+      <c r="F120" t="n">
+        <v>41</v>
+      </c>
+      <c r="G120" t="n">
+        <v>72</v>
+      </c>
+      <c r="H120" t="n">
+        <v>11</v>
+      </c>
+      <c r="I120" t="n">
+        <v>26</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R16</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>15</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>150</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.6866666666666666</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.5223880597014925</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.5982905982905983</v>
+      </c>
+      <c r="F121" t="n">
+        <v>35</v>
+      </c>
+      <c r="G121" t="n">
+        <v>68</v>
+      </c>
+      <c r="H121" t="n">
+        <v>15</v>
+      </c>
+      <c r="I121" t="n">
+        <v>32</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R32</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>15</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>150</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.7066666666666667</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4035087719298245</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5111111111111111</v>
+      </c>
+      <c r="F122" t="n">
+        <v>23</v>
+      </c>
+      <c r="G122" t="n">
+        <v>83</v>
+      </c>
+      <c r="H122" t="n">
+        <v>10</v>
+      </c>
+      <c r="I122" t="n">
+        <v>34</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>16</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>150</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.3928571428571428</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4680851063829787</v>
+      </c>
+      <c r="F123" t="n">
+        <v>33</v>
+      </c>
+      <c r="G123" t="n">
+        <v>42</v>
+      </c>
+      <c r="H123" t="n">
+        <v>51</v>
+      </c>
+      <c r="I123" t="n">
+        <v>24</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R8</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>16</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>150</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.7133333333333334</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4035087719298245</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.5168539325842696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>23</v>
+      </c>
+      <c r="G124" t="n">
+        <v>84</v>
+      </c>
+      <c r="H124" t="n">
+        <v>9</v>
+      </c>
+      <c r="I124" t="n">
+        <v>34</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R16</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>16</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>150</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5894736842105264</v>
+      </c>
+      <c r="F125" t="n">
+        <v>28</v>
+      </c>
+      <c r="G125" t="n">
+        <v>83</v>
+      </c>
+      <c r="H125" t="n">
+        <v>10</v>
+      </c>
+      <c r="I125" t="n">
+        <v>29</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B R32</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>16</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>150</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.6466666666666666</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.3764705882352941</v>
+      </c>
+      <c r="F126" t="n">
+        <v>16</v>
+      </c>
+      <c r="G126" t="n">
+        <v>81</v>
+      </c>
+      <c r="H126" t="n">
+        <v>12</v>
+      </c>
+      <c r="I126" t="n">
+        <v>41</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>16</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>150</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.4565217391304348</v>
+      </c>
+      <c r="F127" t="n">
+        <v>21</v>
+      </c>
+      <c r="G127" t="n">
+        <v>79</v>
+      </c>
+      <c r="H127" t="n">
+        <v>14</v>
+      </c>
+      <c r="I127" t="n">
+        <v>36</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R8</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>16</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>150</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3859649122807017</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4631578947368421</v>
+      </c>
+      <c r="F128" t="n">
+        <v>22</v>
+      </c>
+      <c r="G128" t="n">
+        <v>77</v>
+      </c>
+      <c r="H128" t="n">
+        <v>16</v>
+      </c>
+      <c r="I128" t="n">
+        <v>35</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R16</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>16</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>150</v>
+      </c>
+      <c r="B129" t="n">
         <v>0.6266666666666667</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C129" t="n">
         <v>0.5161290322580645</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D129" t="n">
         <v>0.2807017543859649</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E129" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F129" t="n">
         <v>16</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G129" t="n">
         <v>78</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H129" t="n">
         <v>15</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I129" t="n">
         <v>41</v>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>Llama3.1-8B R32</t>
         </is>
       </c>
-      <c r="K97" t="n">
+      <c r="K129" t="n">
         <v>16</v>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t>List</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>

--- a/eval/qlora/evaluation_metrics_by_qid_full150.xlsx
+++ b/eval/qlora/evaluation_metrics_by_qid_full150.xlsx
@@ -3555,19 +3555,19 @@
         <v>150</v>
       </c>
       <c r="B67" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9252336448598131</v>
+        <v>0.926605504587156</v>
       </c>
       <c r="D67" t="n">
-        <v>0.792</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8534482758620691</v>
+        <v>0.8632478632478633</v>
       </c>
       <c r="F67" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G67" t="n">
         <v>17</v>
@@ -3576,7 +3576,7 @@
         <v>8</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3743,19 +3743,19 @@
         <v>150</v>
       </c>
       <c r="B71" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.64</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="D71" t="n">
-        <v>0.592</v>
+        <v>0.6</v>
       </c>
       <c r="E71" t="n">
-        <v>0.729064039408867</v>
+        <v>0.7352941176470588</v>
       </c>
       <c r="F71" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G71" t="n">
         <v>21</v>
@@ -3764,7 +3764,7 @@
         <v>4</v>
       </c>
       <c r="I71" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4119,19 +4119,19 @@
         <v>150</v>
       </c>
       <c r="B79" t="n">
-        <v>0.76</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8813559322033898</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="D79" t="n">
-        <v>0.6419753086419753</v>
+        <v>0.654320987654321</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7428571428571428</v>
+        <v>0.75177304964539</v>
       </c>
       <c r="F79" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G79" t="n">
         <v>62</v>
@@ -4140,7 +4140,7 @@
         <v>7</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
